--- a/research/traditional_assets/database/data/malaysia/malaysia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09855</v>
+        <v>0.0536</v>
       </c>
       <c r="E2">
-        <v>0.139</v>
+        <v>0.06265</v>
       </c>
       <c r="G2">
-        <v>0.2307734755817162</v>
+        <v>0.2191344811540251</v>
       </c>
       <c r="H2">
-        <v>0.2307734755817162</v>
+        <v>0.2191344811540251</v>
       </c>
       <c r="I2">
-        <v>0.2247401821024556</v>
+        <v>0.1294741740344346</v>
       </c>
       <c r="J2">
-        <v>0.1786896060093134</v>
+        <v>0.1016500089920536</v>
       </c>
       <c r="K2">
-        <v>268.88</v>
+        <v>165.48</v>
       </c>
       <c r="L2">
-        <v>0.4945829117998712</v>
+        <v>0.308013029315961</v>
       </c>
       <c r="M2">
-        <v>161.16</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N2">
-        <v>0.06305164319248827</v>
+        <v>0.04027200912126395</v>
       </c>
       <c r="O2">
-        <v>0.5993751859565606</v>
+        <v>0.5976553057771331</v>
       </c>
       <c r="P2">
-        <v>161.16</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.06305164319248827</v>
+        <v>0.04027200912126395</v>
       </c>
       <c r="R2">
-        <v>0.5993751859565606</v>
+        <v>0.5976553057771331</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>157.36</v>
+        <v>167.8</v>
       </c>
       <c r="V2">
-        <v>0.06156494522691705</v>
+        <v>0.06832803974265005</v>
       </c>
       <c r="W2">
-        <v>0.2533333333333333</v>
+        <v>0.1199548590483962</v>
       </c>
       <c r="X2">
-        <v>0.0282215284131609</v>
+        <v>0.05356455433179103</v>
       </c>
       <c r="Y2">
-        <v>0.2251118049201724</v>
+        <v>0.06639030471660515</v>
       </c>
       <c r="Z2">
-        <v>0.1689608125285538</v>
+        <v>0.1695030225015459</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02746867603918612</v>
+        <v>0.05248768540545445</v>
       </c>
       <c r="AC2">
-        <v>-0.02965416679967402</v>
+        <v>-0.05369765438989438</v>
       </c>
       <c r="AD2">
-        <v>2273.911</v>
+        <v>2210.116</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2273.911</v>
+        <v>2210.116</v>
       </c>
       <c r="AG2">
-        <v>2116.551</v>
+        <v>2042.316</v>
       </c>
       <c r="AH2">
-        <v>0.4707977020694584</v>
+        <v>0.4736724793159585</v>
       </c>
       <c r="AI2">
-        <v>0.6842511655143173</v>
+        <v>0.6677660560603991</v>
       </c>
       <c r="AJ2">
-        <v>0.4529754731409031</v>
+        <v>0.454038090613937</v>
       </c>
       <c r="AK2">
-        <v>0.6685567324551914</v>
+        <v>0.6500224703652167</v>
       </c>
       <c r="AL2">
-        <v>1.08</v>
+        <v>0.455</v>
       </c>
       <c r="AM2">
-        <v>1.08</v>
+        <v>0.455</v>
       </c>
       <c r="AN2">
-        <v>18.16803291786513</v>
+        <v>29.90684709066306</v>
       </c>
       <c r="AO2">
-        <v>113.1296296296296</v>
+        <v>152.8791208791209</v>
       </c>
       <c r="AP2">
-        <v>16.91076222435283</v>
+        <v>27.63621109607578</v>
       </c>
       <c r="AQ2">
-        <v>113.1296296296296</v>
+        <v>152.8791208791209</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.0317</v>
       </c>
       <c r="E3">
-        <v>0.153</v>
+        <v>0.0216</v>
       </c>
       <c r="G3">
-        <v>0.6562657272269754</v>
+        <v>0.8855646970830218</v>
       </c>
       <c r="H3">
-        <v>0.6562657272269754</v>
+        <v>0.8855646970830218</v>
       </c>
       <c r="I3">
-        <v>0.6406643180674384</v>
+        <v>0.5325355272999253</v>
       </c>
       <c r="J3">
-        <v>0.4792290937049619</v>
+        <v>0.3885868483519063</v>
       </c>
       <c r="K3">
-        <v>94.5</v>
+        <v>52.2</v>
       </c>
       <c r="L3">
-        <v>0.4755913437342728</v>
+        <v>0.3904263275991025</v>
       </c>
       <c r="M3">
-        <v>112.2</v>
+        <v>55.7</v>
       </c>
       <c r="N3">
-        <v>0.08818674840839426</v>
+        <v>0.04533246520712949</v>
       </c>
       <c r="O3">
-        <v>1.187301587301587</v>
+        <v>1.067049808429119</v>
       </c>
       <c r="P3">
-        <v>112.2</v>
+        <v>55.7</v>
       </c>
       <c r="Q3">
-        <v>0.08818674840839426</v>
+        <v>0.04533246520712949</v>
       </c>
       <c r="R3">
-        <v>1.187301587301587</v>
+        <v>1.067049808429119</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,70 +773,70 @@
         <v>121.6</v>
       </c>
       <c r="V3">
-        <v>0.09557494301658413</v>
+        <v>0.0989663872385448</v>
       </c>
       <c r="W3">
-        <v>0.4978925184404636</v>
+        <v>0.2934232715008432</v>
       </c>
       <c r="X3">
-        <v>0.02527643414568621</v>
+        <v>0.05141477123678841</v>
       </c>
       <c r="Y3">
-        <v>0.4726160842947774</v>
+        <v>0.2420085002640548</v>
       </c>
       <c r="Z3">
-        <v>3.61864869786924</v>
+        <v>2.785416666666666</v>
       </c>
       <c r="AA3">
-        <v>1.734161735916516</v>
+        <v>1.082376283846872</v>
       </c>
       <c r="AB3">
-        <v>0.02527678830040825</v>
+        <v>0.05140845357136071</v>
       </c>
       <c r="AC3">
-        <v>1.708884947616108</v>
+        <v>1.030967830275511</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>-119.6</v>
+        <v>-119.8</v>
       </c>
       <c r="AH3">
-        <v>0.001569489131287766</v>
+        <v>0.001462819991873222</v>
       </c>
       <c r="AI3">
-        <v>0.01111728738187882</v>
+        <v>0.01125</v>
       </c>
       <c r="AJ3">
-        <v>-0.1037563980220352</v>
+        <v>-0.1080349896293624</v>
       </c>
       <c r="AK3">
-        <v>-2.051457975986277</v>
+        <v>-3.119791666666667</v>
       </c>
       <c r="AL3">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="AM3">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="AN3">
-        <v>0.0153727901614143</v>
+        <v>0.02406417112299465</v>
       </c>
       <c r="AO3">
-        <v>994.53125</v>
+        <v>619.1304347826087</v>
       </c>
       <c r="AP3">
-        <v>-0.9192928516525749</v>
+        <v>-1.601604278074866</v>
       </c>
       <c r="AQ3">
-        <v>994.53125</v>
+        <v>619.1304347826087</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ELK-Desa Resources Berhad (KLSE:ELKDESA)</t>
+          <t>Pappajack Berhad (KLSE:PPJACK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,110 +855,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.106</v>
-      </c>
-      <c r="E4">
-        <v>0.09710000000000001</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1644970414201183</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1644970414201183</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.1414201183431953</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.1030166995397765</v>
       </c>
       <c r="K4">
-        <v>7.88</v>
+        <v>1.64</v>
       </c>
       <c r="L4">
-        <v>0.3126984126984127</v>
+        <v>0.0970414201183432</v>
       </c>
       <c r="M4">
-        <v>5.16</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.05471898197242842</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6548223350253808</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>5.16</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.05471898197242842</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6548223350253808</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>3.6</v>
+        <v>3.93</v>
       </c>
       <c r="V4">
-        <v>0.03817603393425239</v>
+        <v>0.04559164733178654</v>
       </c>
       <c r="W4">
-        <v>0.0768780487804878</v>
+        <v>0.06096654275092937</v>
       </c>
       <c r="X4">
-        <v>0.0282215284131609</v>
+        <v>0.05187512623737911</v>
       </c>
       <c r="Y4">
-        <v>0.04865652036732691</v>
+        <v>0.009091416513550256</v>
       </c>
       <c r="Z4">
-        <v>0.1730769230769231</v>
+        <v>0.6161137440758293</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.06347000445578646</v>
       </c>
       <c r="AB4">
-        <v>0.02746867603918612</v>
+        <v>0.05206206882520403</v>
       </c>
       <c r="AC4">
-        <v>-0.02746867603918612</v>
+        <v>0.01140793563058243</v>
       </c>
       <c r="AD4">
-        <v>36.1</v>
+        <v>4.27</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>36.1</v>
+        <v>4.27</v>
       </c>
       <c r="AG4">
-        <v>32.5</v>
+        <v>0.3399999999999994</v>
       </c>
       <c r="AH4">
-        <v>0.276840490797546</v>
+        <v>0.04719796617663313</v>
       </c>
       <c r="AI4">
-        <v>0.2565742714996447</v>
+        <v>0.1034649866731282</v>
       </c>
       <c r="AJ4">
-        <v>0.2563091482649842</v>
+        <v>0.003928819043217002</v>
       </c>
       <c r="AK4">
-        <v>0.2370532458059811</v>
+        <v>0.009105516871987131</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.138</v>
+      </c>
+      <c r="AN4">
+        <v>1.525</v>
+      </c>
+      <c r="AO4">
+        <v>17.31884057971014</v>
+      </c>
+      <c r="AP4">
+        <v>0.1214285714285712</v>
+      </c>
+      <c r="AQ4">
+        <v>17.31884057971014</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RCE Capital Berhad (KLSE:RCECAP)</t>
+          <t>ELK-Desa Resources Berhad (KLSE:ELKDESA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,10 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0951</v>
+        <v>0.122</v>
       </c>
       <c r="E5">
-        <v>0.194</v>
+        <v>0.144</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,28 +999,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>32.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L5">
-        <v>0.5898366606170599</v>
+        <v>0.3261744966442953</v>
       </c>
       <c r="M5">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="N5">
-        <v>0.0338368580060423</v>
+        <v>0.03088101725703906</v>
       </c>
       <c r="O5">
-        <v>0.3446153846153846</v>
+        <v>0.3497942386831275</v>
       </c>
       <c r="P5">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>0.0338368580060423</v>
+        <v>0.03088101725703906</v>
       </c>
       <c r="R5">
-        <v>0.3446153846153846</v>
+        <v>0.3497942386831275</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,55 +1029,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.65</v>
+        <v>7.73</v>
       </c>
       <c r="V5">
-        <v>0.01102719033232628</v>
+        <v>0.07020890099909174</v>
       </c>
       <c r="W5">
-        <v>0.1882966396292005</v>
+        <v>0.09292543021032505</v>
       </c>
       <c r="X5">
-        <v>0.03475583491161668</v>
+        <v>0.05525398242620295</v>
       </c>
       <c r="Y5">
-        <v>0.1535408047175838</v>
+        <v>0.0376714477841221</v>
       </c>
       <c r="Z5">
-        <v>0.106145251396648</v>
+        <v>0.2173595915390226</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02965416679967402</v>
+        <v>0.05291330198570489</v>
       </c>
       <c r="AC5">
-        <v>-0.02965416679967402</v>
+        <v>-0.05291330198570489</v>
       </c>
       <c r="AD5">
-        <v>406.7</v>
+        <v>44.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>406.7</v>
+        <v>44.3</v>
       </c>
       <c r="AG5">
-        <v>403.05</v>
+        <v>36.56999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.55130811983191</v>
+        <v>0.2869170984455959</v>
       </c>
       <c r="AI5">
-        <v>0.6733443708609271</v>
+        <v>0.3061506565307533</v>
       </c>
       <c r="AJ5">
-        <v>0.5490770383488863</v>
+        <v>0.2493352423808549</v>
       </c>
       <c r="AK5">
-        <v>0.671358374281669</v>
+        <v>0.2669927721398846</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AEON Credit Service (M) Berhad (KLSE:AEONCR)</t>
+          <t>RCE Capital Berhad (KLSE:RCECAP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,10 +1103,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.04269999999999999</v>
+        <v>0.0451</v>
       </c>
       <c r="E6">
-        <v>0.125</v>
+        <v>0.095</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,28 +1121,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>108.3</v>
+        <v>29</v>
       </c>
       <c r="L6">
-        <v>0.4215648112105878</v>
+        <v>0.5906313645621181</v>
       </c>
       <c r="M6">
-        <v>32.6</v>
+        <v>11.8</v>
       </c>
       <c r="N6">
-        <v>0.03906062784567457</v>
+        <v>0.04172560113154172</v>
       </c>
       <c r="O6">
-        <v>0.3010156971375808</v>
+        <v>0.406896551724138</v>
       </c>
       <c r="P6">
-        <v>32.6</v>
+        <v>11.8</v>
       </c>
       <c r="Q6">
-        <v>0.03906062784567457</v>
+        <v>0.04172560113154172</v>
       </c>
       <c r="R6">
-        <v>0.3010156971375808</v>
+        <v>0.406896551724138</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1148,55 +1151,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>7.61</v>
+        <v>17.8</v>
       </c>
       <c r="V6">
-        <v>0.009118140426551642</v>
+        <v>0.06294200848656294</v>
       </c>
       <c r="W6">
-        <v>0.2533333333333333</v>
+        <v>0.1469842878864673</v>
       </c>
       <c r="X6">
-        <v>0.04218753105310974</v>
+        <v>0.06487159448833518</v>
       </c>
       <c r="Y6">
-        <v>0.2111458022802236</v>
+        <v>0.08211269339813212</v>
       </c>
       <c r="Z6">
-        <v>0.1072293179731196</v>
+        <v>0.08335455394278923</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03073140198494677</v>
+        <v>0.05448200679408387</v>
       </c>
       <c r="AC6">
-        <v>-0.03073140198494677</v>
+        <v>-0.05448200679408387</v>
       </c>
       <c r="AD6">
-        <v>1828.4</v>
+        <v>397.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1828.4</v>
+        <v>397.8</v>
       </c>
       <c r="AG6">
-        <v>1820.79</v>
+        <v>380</v>
       </c>
       <c r="AH6">
-        <v>0.6865940668419076</v>
+        <v>0.5844842785777256</v>
       </c>
       <c r="AI6">
-        <v>0.7817684282538053</v>
+        <v>0.6696969696969697</v>
       </c>
       <c r="AJ6">
-        <v>0.6856958864799521</v>
+        <v>0.5733252866626434</v>
       </c>
       <c r="AK6">
-        <v>0.7810560271792518</v>
+        <v>0.6594932315168344</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,121 +1216,243 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>AEON Credit Service (M) Berhad (KLSE:AEONCR)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0621</v>
+      </c>
+      <c r="E7">
+        <v>0.0303</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0.2575206611570248</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+      <c r="N7">
+        <v>0.03818355379789991</v>
+      </c>
+      <c r="O7">
+        <v>0.3594351732991014</v>
+      </c>
+      <c r="P7">
+        <v>28</v>
+      </c>
+      <c r="Q7">
+        <v>0.03818355379789991</v>
+      </c>
+      <c r="R7">
+        <v>0.3594351732991014</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>7.8</v>
+      </c>
+      <c r="V7">
+        <v>0.01063684712941497</v>
+      </c>
+      <c r="W7">
+        <v>0.1526253918495298</v>
+      </c>
+      <c r="X7">
+        <v>0.07440382332283318</v>
+      </c>
+      <c r="Y7">
+        <v>0.07822156852669662</v>
+      </c>
+      <c r="Z7">
+        <v>0.1297687884828806</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05512290900101632</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05512290900101632</v>
+      </c>
+      <c r="AD7">
+        <v>1761.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>1761.4</v>
+      </c>
+      <c r="AG7">
+        <v>1753.6</v>
+      </c>
+      <c r="AH7">
+        <v>0.706056840501864</v>
+      </c>
+      <c r="AI7">
+        <v>0.7605025689737057</v>
+      </c>
+      <c r="AJ7">
+        <v>0.70513490691222</v>
+      </c>
+      <c r="AK7">
+        <v>0.7596932807693973</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Johan Holdings Berhad (KLSE:JOHAN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G7">
-        <v>-0.6374193548387097</v>
-      </c>
-      <c r="H7">
-        <v>-0.6374193548387097</v>
-      </c>
-      <c r="I7">
-        <v>-0.6606451612903226</v>
-      </c>
-      <c r="J7">
-        <v>-0.6606451612903226</v>
-      </c>
-      <c r="K7">
-        <v>25.7</v>
-      </c>
-      <c r="L7">
-        <v>3.316129032258064</v>
-      </c>
-      <c r="M7">
+      <c r="G8">
+        <v>-0.6571428571428571</v>
+      </c>
+      <c r="H8">
+        <v>-0.6571428571428571</v>
+      </c>
+      <c r="I8">
+        <v>-0.7676190476190476</v>
+      </c>
+      <c r="J8">
+        <v>-0.7676190476190476</v>
+      </c>
+      <c r="K8">
+        <v>-4.98</v>
+      </c>
+      <c r="L8">
+        <v>-0.9485714285714286</v>
+      </c>
+      <c r="M8">
         <v>-0</v>
       </c>
-      <c r="N7">
+      <c r="N8">
         <v>-0</v>
       </c>
-      <c r="O7">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>-0</v>
       </c>
-      <c r="P7">
+      <c r="Q8">
         <v>-0</v>
       </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>20.9</v>
-      </c>
-      <c r="V7">
-        <v>0.8781512605042016</v>
-      </c>
-      <c r="W7">
-        <v>2.357798165137615</v>
-      </c>
-      <c r="X7">
-        <v>0.02549506311435984</v>
-      </c>
-      <c r="Y7">
-        <v>2.332303102023255</v>
-      </c>
-      <c r="Z7">
-        <v>0.07583170254403129</v>
-      </c>
-      <c r="AA7">
-        <v>-0.05009784735812133</v>
-      </c>
-      <c r="AB7">
-        <v>0.02559706950423082</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07569491686235215</v>
-      </c>
-      <c r="AD7">
-        <v>0.711</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.711</v>
-      </c>
-      <c r="AG7">
-        <v>-20.189</v>
-      </c>
-      <c r="AH7">
-        <v>0.02900738443963935</v>
-      </c>
-      <c r="AI7">
-        <v>0.01188744545317751</v>
-      </c>
-      <c r="AJ7">
-        <v>-5.590972029908611</v>
-      </c>
-      <c r="AK7">
-        <v>-0.5188507105959754</v>
-      </c>
-      <c r="AL7">
-        <v>0.952</v>
-      </c>
-      <c r="AM7">
-        <v>0.952</v>
-      </c>
-      <c r="AN7">
-        <v>-0.1439271255060729</v>
-      </c>
-      <c r="AO7">
-        <v>-5.378151260504202</v>
-      </c>
-      <c r="AP7">
-        <v>4.086842105263157</v>
-      </c>
-      <c r="AQ7">
-        <v>-5.378151260504202</v>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>8.94</v>
+      </c>
+      <c r="V8">
+        <v>0.6081632653061224</v>
+      </c>
+      <c r="W8">
+        <v>-0.08721541155866901</v>
+      </c>
+      <c r="X8">
+        <v>0.05175644286885151</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1389718544275205</v>
+      </c>
+      <c r="Z8">
+        <v>0.1422340223781529</v>
+      </c>
+      <c r="AA8">
+        <v>-0.109181544796944</v>
+      </c>
+      <c r="AB8">
+        <v>0.05179911374242892</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1609806585393729</v>
+      </c>
+      <c r="AD8">
+        <v>0.546</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.546</v>
+      </c>
+      <c r="AG8">
+        <v>-8.394</v>
+      </c>
+      <c r="AH8">
+        <v>0.03581267217630855</v>
+      </c>
+      <c r="AI8">
+        <v>0.01017783245721955</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.331113225499524</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1877600322104415</v>
+      </c>
+      <c r="AL8">
+        <v>0.202</v>
+      </c>
+      <c r="AM8">
+        <v>0.202</v>
+      </c>
+      <c r="AN8">
+        <v>-0.1475675675675676</v>
+      </c>
+      <c r="AO8">
+        <v>-19.95049504950495</v>
+      </c>
+      <c r="AP8">
+        <v>2.268648648648649</v>
+      </c>
+      <c r="AQ8">
+        <v>-19.95049504950495</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0536</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="E2">
-        <v>0.06265</v>
+        <v>0.02695</v>
       </c>
       <c r="G2">
-        <v>0.2191344811540251</v>
+        <v>0.1214951413427562</v>
       </c>
       <c r="H2">
-        <v>0.2191344811540251</v>
+        <v>0.1213339222614841</v>
       </c>
       <c r="I2">
-        <v>0.1294741740344346</v>
+        <v>0.09306455270445854</v>
       </c>
       <c r="J2">
-        <v>0.1016500089920536</v>
+        <v>0.07859611292990808</v>
       </c>
       <c r="K2">
-        <v>165.48</v>
+        <v>169.14</v>
       </c>
       <c r="L2">
-        <v>0.308013029315961</v>
+        <v>0.1867712014134275</v>
       </c>
       <c r="M2">
-        <v>98.90000000000001</v>
+        <v>150.8342</v>
       </c>
       <c r="N2">
-        <v>0.04027200912126395</v>
+        <v>0.04219256482698817</v>
       </c>
       <c r="O2">
-        <v>0.5976553057771331</v>
+        <v>0.8917713137046235</v>
       </c>
       <c r="P2">
-        <v>98.90000000000001</v>
+        <v>150.7482</v>
       </c>
       <c r="Q2">
-        <v>0.04027200912126395</v>
+        <v>0.04216850821001986</v>
       </c>
       <c r="R2">
-        <v>0.5976553057771331</v>
+        <v>0.8912628591699184</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.0860000000000003</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.000570162469784706</v>
       </c>
       <c r="U2">
-        <v>167.8</v>
+        <v>309.05</v>
       </c>
       <c r="V2">
-        <v>0.06832803974265005</v>
+        <v>0.08644997062854905</v>
       </c>
       <c r="W2">
-        <v>0.1199548590483962</v>
+        <v>0.05779816513761468</v>
       </c>
       <c r="X2">
-        <v>0.05356455433179103</v>
+        <v>0.05551416551240074</v>
       </c>
       <c r="Y2">
-        <v>0.06639030471660515</v>
+        <v>0.002283999625213938</v>
       </c>
       <c r="Z2">
-        <v>0.1695030225015459</v>
+        <v>0.2538285404017897</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.0349279037274198</v>
       </c>
       <c r="AB2">
-        <v>0.05248768540545445</v>
+        <v>0.05453377066921195</v>
       </c>
       <c r="AC2">
-        <v>-0.05369765438989438</v>
+        <v>-0.01973750467683695</v>
       </c>
       <c r="AD2">
-        <v>2210.116</v>
+        <v>2547.529</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.3837053542117431</v>
       </c>
       <c r="AF2">
-        <v>2210.116</v>
+        <v>2547.912705354212</v>
       </c>
       <c r="AG2">
-        <v>2042.316</v>
+        <v>2238.862705354212</v>
       </c>
       <c r="AH2">
-        <v>0.4736724793159585</v>
+        <v>0.4161343532729885</v>
       </c>
       <c r="AI2">
-        <v>0.6677660560603991</v>
+        <v>0.6088765878128118</v>
       </c>
       <c r="AJ2">
-        <v>0.454038090613937</v>
+        <v>0.3850970221561195</v>
       </c>
       <c r="AK2">
-        <v>0.6500224703652167</v>
+        <v>0.5776871323127226</v>
       </c>
       <c r="AL2">
-        <v>0.455</v>
+        <v>4.533</v>
       </c>
       <c r="AM2">
-        <v>0.455</v>
+        <v>2.228</v>
       </c>
       <c r="AN2">
-        <v>29.90684709066306</v>
+        <v>23.62191458190383</v>
       </c>
       <c r="AO2">
-        <v>152.8791208791209</v>
+        <v>18.5197440988308</v>
       </c>
       <c r="AP2">
-        <v>27.63621109607578</v>
+        <v>20.75981218917913</v>
       </c>
       <c r="AQ2">
-        <v>152.8791208791209</v>
+        <v>37.67953321364453</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0317</v>
+        <v>0.0155</v>
       </c>
       <c r="E3">
-        <v>0.0216</v>
+        <v>0.0123</v>
       </c>
       <c r="G3">
-        <v>0.8855646970830218</v>
+        <v>0.5774319066147861</v>
       </c>
       <c r="H3">
-        <v>0.8855646970830218</v>
+        <v>0.5774319066147861</v>
       </c>
       <c r="I3">
-        <v>0.5325355272999253</v>
+        <v>0.5284046692607004</v>
       </c>
       <c r="J3">
-        <v>0.3885868483519063</v>
+        <v>0.4025568116409182</v>
       </c>
       <c r="K3">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="L3">
-        <v>0.3904263275991025</v>
+        <v>0.4007782101167315</v>
       </c>
       <c r="M3">
-        <v>55.7</v>
+        <v>45.7</v>
       </c>
       <c r="N3">
-        <v>0.04533246520712949</v>
+        <v>0.03748974569319114</v>
       </c>
       <c r="O3">
-        <v>1.067049808429119</v>
+        <v>0.887378640776699</v>
       </c>
       <c r="P3">
-        <v>55.7</v>
+        <v>45.7</v>
       </c>
       <c r="Q3">
-        <v>0.04533246520712949</v>
+        <v>0.03748974569319114</v>
       </c>
       <c r="R3">
-        <v>1.067049808429119</v>
+        <v>0.887378640776699</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>121.6</v>
+        <v>117.4</v>
       </c>
       <c r="V3">
-        <v>0.0989663872385448</v>
+        <v>0.0963084495488105</v>
       </c>
       <c r="W3">
-        <v>0.2934232715008432</v>
+        <v>0.3255372945638433</v>
       </c>
       <c r="X3">
-        <v>0.05141477123678841</v>
+        <v>0.05403324869546051</v>
       </c>
       <c r="Y3">
-        <v>0.2420085002640548</v>
+        <v>0.2715040458683828</v>
       </c>
       <c r="Z3">
-        <v>2.785416666666666</v>
+        <v>4.406721536351165</v>
       </c>
       <c r="AA3">
-        <v>1.082376283846872</v>
+        <v>1.773955771462894</v>
       </c>
       <c r="AB3">
-        <v>0.05140845357136071</v>
+        <v>0.05401885077672696</v>
       </c>
       <c r="AC3">
-        <v>1.030967830275511</v>
+        <v>1.719936920686167</v>
       </c>
       <c r="AD3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>-119.8</v>
+        <v>-115.62</v>
       </c>
       <c r="AH3">
-        <v>0.001462819991873222</v>
+        <v>0.001458084175690952</v>
       </c>
       <c r="AI3">
-        <v>0.01125</v>
+        <v>0.01078918656806886</v>
       </c>
       <c r="AJ3">
-        <v>-0.1080349896293624</v>
+        <v>-0.1047871087023509</v>
       </c>
       <c r="AK3">
-        <v>-3.119791666666667</v>
+        <v>-2.43001261034048</v>
       </c>
       <c r="AL3">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="AM3">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="AN3">
-        <v>0.02406417112299465</v>
+        <v>0.02451790633608816</v>
       </c>
       <c r="AO3">
-        <v>619.1304347826087</v>
+        <v>595.6140350877193</v>
       </c>
       <c r="AP3">
-        <v>-1.601604278074866</v>
+        <v>-1.592561983471074</v>
       </c>
       <c r="AQ3">
-        <v>619.1304347826087</v>
+        <v>595.6140350877193</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pappajack Berhad (KLSE:PPJACK)</t>
+          <t>GHL Systems Berhad (KLSE:GHLSYS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,113 +855,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>0.0584</v>
+      </c>
       <c r="G4">
-        <v>0.1644970414201183</v>
+        <v>0.1586617492096944</v>
       </c>
       <c r="H4">
-        <v>0.1644970414201183</v>
+        <v>0.1580611169652265</v>
       </c>
       <c r="I4">
-        <v>0.1414201183431953</v>
+        <v>0.1044257112750263</v>
       </c>
       <c r="J4">
-        <v>0.1030166995397765</v>
+        <v>0.07089245485265797</v>
       </c>
       <c r="K4">
-        <v>1.64</v>
+        <v>6.3</v>
       </c>
       <c r="L4">
-        <v>0.0970414201183432</v>
+        <v>0.06638566912539515</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>6.08</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03516483516483516</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.9650793650793651</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>6.08</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03516483516483516</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.9650793650793651</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>3.93</v>
+        <v>40.3</v>
       </c>
       <c r="V4">
-        <v>0.04559164733178654</v>
+        <v>0.2330827067669173</v>
       </c>
       <c r="W4">
-        <v>0.06096654275092937</v>
+        <v>0.05545774647887324</v>
       </c>
       <c r="X4">
-        <v>0.05187512623737911</v>
+        <v>0.054732032812966</v>
       </c>
       <c r="Y4">
-        <v>0.009091416513550256</v>
+        <v>0.0007257136659072419</v>
       </c>
       <c r="Z4">
-        <v>0.6161137440758293</v>
+        <v>2.279606053326928</v>
       </c>
       <c r="AA4">
-        <v>0.06347000445578646</v>
+        <v>0.1616068692173251</v>
       </c>
       <c r="AB4">
-        <v>0.05206206882520403</v>
+        <v>0.05437325588290425</v>
       </c>
       <c r="AC4">
-        <v>0.01140793563058243</v>
+        <v>0.1072336133344208</v>
       </c>
       <c r="AD4">
-        <v>4.27</v>
+        <v>10.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.27</v>
+        <v>10.7</v>
       </c>
       <c r="AG4">
-        <v>0.3399999999999994</v>
+        <v>-29.6</v>
       </c>
       <c r="AH4">
-        <v>0.04719796617663313</v>
+        <v>0.05827886710239651</v>
       </c>
       <c r="AI4">
-        <v>0.1034649866731282</v>
+        <v>0.0859437751004016</v>
       </c>
       <c r="AJ4">
-        <v>0.003928819043217002</v>
+        <v>-0.206559665038381</v>
       </c>
       <c r="AK4">
-        <v>0.009105516871987131</v>
+        <v>-0.3515439429928741</v>
       </c>
       <c r="AL4">
-        <v>0.138</v>
+        <v>0.336</v>
       </c>
       <c r="AM4">
-        <v>0.138</v>
+        <v>0.336</v>
       </c>
       <c r="AN4">
-        <v>1.525</v>
+        <v>0.7588652482269503</v>
       </c>
       <c r="AO4">
-        <v>17.31884057971014</v>
+        <v>29.49404761904762</v>
       </c>
       <c r="AP4">
-        <v>0.1214285714285712</v>
+        <v>-2.099290780141844</v>
       </c>
       <c r="AQ4">
-        <v>17.31884057971014</v>
+        <v>29.49404761904762</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ELK-Desa Resources Berhad (KLSE:ELKDESA)</t>
+          <t>Pappajack Berhad (KLSE:PPJACK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -980,47 +989,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.122</v>
-      </c>
-      <c r="E5">
-        <v>0.144</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1709677419354839</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.1709677419354839</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.2806451612903226</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.1989134125636672</v>
       </c>
       <c r="K5">
-        <v>9.720000000000001</v>
+        <v>4.03</v>
       </c>
       <c r="L5">
-        <v>0.3261744966442953</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="M5">
-        <v>3.4</v>
+        <v>0.7682000000000001</v>
       </c>
       <c r="N5">
-        <v>0.03088101725703906</v>
+        <v>0.004369738339021616</v>
       </c>
       <c r="O5">
-        <v>0.3497942386831275</v>
+        <v>0.190620347394541</v>
       </c>
       <c r="P5">
-        <v>3.4</v>
+        <v>0.7682000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.03088101725703906</v>
+        <v>0.004369738339021616</v>
       </c>
       <c r="R5">
-        <v>0.3497942386831275</v>
+        <v>0.190620347394541</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,61 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7.73</v>
+        <v>12.2</v>
       </c>
       <c r="V5">
-        <v>0.07020890099909174</v>
+        <v>0.06939704209328781</v>
       </c>
       <c r="W5">
-        <v>0.09292543021032505</v>
+        <v>0.1095108695652174</v>
       </c>
       <c r="X5">
-        <v>0.05525398242620295</v>
+        <v>0.05455906175925537</v>
       </c>
       <c r="Y5">
-        <v>0.0376714477841221</v>
+        <v>0.05495180780596204</v>
       </c>
       <c r="Z5">
-        <v>0.2173595915390226</v>
+        <v>0.5842757135164244</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.1162202760536236</v>
       </c>
       <c r="AB5">
-        <v>0.05291330198570489</v>
+        <v>0.05429086442553702</v>
       </c>
       <c r="AC5">
-        <v>-0.05291330198570489</v>
+        <v>0.06192941162808657</v>
       </c>
       <c r="AD5">
-        <v>44.3</v>
+        <v>8.25</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>44.3</v>
+        <v>8.25</v>
       </c>
       <c r="AG5">
-        <v>36.56999999999999</v>
+        <v>-3.949999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2869170984455959</v>
+        <v>0.04482477587612062</v>
       </c>
       <c r="AI5">
-        <v>0.3061506565307533</v>
+        <v>0.1371571072319202</v>
       </c>
       <c r="AJ5">
-        <v>0.2493352423808549</v>
+        <v>-0.02298516147803316</v>
       </c>
       <c r="AK5">
-        <v>0.2669927721398846</v>
+        <v>-0.08237747653806046</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.407</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="AN5">
+        <v>1.293103448275862</v>
+      </c>
+      <c r="AO5">
+        <v>14.96314496314496</v>
+      </c>
+      <c r="AP5">
+        <v>-0.6191222570532914</v>
+      </c>
+      <c r="AQ5">
+        <v>15.81818181818182</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RCE Capital Berhad (KLSE:RCECAP)</t>
+          <t>MTAG Group Berhad (KLSE:MTAG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1102,47 +1117,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0451</v>
-      </c>
-      <c r="E6">
-        <v>0.095</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.2893772893772894</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.2893772893772894</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.2021978021978022</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.1548122910568325</v>
       </c>
       <c r="K6">
-        <v>29</v>
+        <v>5.26</v>
       </c>
       <c r="L6">
-        <v>0.5906313645621181</v>
+        <v>0.1926739926739927</v>
       </c>
       <c r="M6">
-        <v>11.8</v>
+        <v>4.36</v>
       </c>
       <c r="N6">
-        <v>0.04172560113154172</v>
+        <v>0.06449704142011835</v>
       </c>
       <c r="O6">
-        <v>0.406896551724138</v>
+        <v>0.8288973384030419</v>
       </c>
       <c r="P6">
-        <v>11.8</v>
+        <v>4.36</v>
       </c>
       <c r="Q6">
-        <v>0.04172560113154172</v>
+        <v>0.06449704142011835</v>
       </c>
       <c r="R6">
-        <v>0.406896551724138</v>
+        <v>0.8288973384030419</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,61 +1160,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>17.8</v>
+        <v>5.33</v>
       </c>
       <c r="V6">
-        <v>0.06294200848656294</v>
+        <v>0.07884615384615386</v>
       </c>
       <c r="W6">
-        <v>0.1469842878864673</v>
+        <v>0.1136069114470842</v>
       </c>
       <c r="X6">
-        <v>0.06487159448833518</v>
+        <v>0.05404595752764171</v>
       </c>
       <c r="Y6">
-        <v>0.08211269339813212</v>
+        <v>0.05956095391944252</v>
       </c>
       <c r="Z6">
-        <v>0.08335455394278923</v>
+        <v>0.6333518930957684</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.09805065761533796</v>
       </c>
       <c r="AB6">
-        <v>0.05448200679408387</v>
+        <v>0.05403199424930161</v>
       </c>
       <c r="AC6">
-        <v>-0.05448200679408387</v>
+        <v>0.04401866336603635</v>
       </c>
       <c r="AD6">
-        <v>397.8</v>
+        <v>0.173</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>397.8</v>
+        <v>0.173</v>
       </c>
       <c r="AG6">
-        <v>380</v>
+        <v>-5.157</v>
       </c>
       <c r="AH6">
-        <v>0.5844842785777256</v>
+        <v>0.002552638956516607</v>
       </c>
       <c r="AI6">
-        <v>0.6696969696969697</v>
+        <v>0.003667352086998919</v>
       </c>
       <c r="AJ6">
-        <v>0.5733252866626434</v>
+        <v>-0.08258731963550758</v>
       </c>
       <c r="AK6">
-        <v>0.6594932315168344</v>
+        <v>-0.1232464211457113</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.623</v>
+      </c>
+      <c r="AN6">
+        <v>0.02836065573770492</v>
+      </c>
+      <c r="AO6">
+        <v>368</v>
+      </c>
+      <c r="AP6">
+        <v>-0.8454098360655738</v>
+      </c>
+      <c r="AQ6">
+        <v>-8.860353130016051</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEON Credit Service (M) Berhad (KLSE:AEONCR)</t>
+          <t>Evergreen Max Cash Capital Berhad (KLSE:EMCC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1224,110 +1245,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0621</v>
-      </c>
-      <c r="E7">
-        <v>0.0303</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.2112195121951219</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.2112195121951219</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.2317073170731707</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.1884812461569994</v>
       </c>
       <c r="K7">
-        <v>77.90000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="L7">
-        <v>0.2575206611570248</v>
+        <v>0.2360975609756097</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03818355379789991</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.3594351732991014</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>28</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03818355379789991</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.3594351732991014</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>7.8</v>
+        <v>12.9</v>
       </c>
       <c r="V7">
-        <v>0.01063684712941497</v>
+        <v>0.1295180722891566</v>
       </c>
       <c r="W7">
-        <v>0.1526253918495298</v>
+        <v>0.1868725868725869</v>
       </c>
       <c r="X7">
-        <v>0.07440382332283318</v>
+        <v>0.05551416551240074</v>
       </c>
       <c r="Y7">
-        <v>0.07822156852669662</v>
+        <v>0.1313584213601861</v>
       </c>
       <c r="Z7">
-        <v>0.1297687884828806</v>
+        <v>0.5222929936305732</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.09844243429856019</v>
       </c>
       <c r="AB7">
-        <v>0.05512290900101632</v>
+        <v>0.05495116336449759</v>
       </c>
       <c r="AC7">
-        <v>-0.05512290900101632</v>
+        <v>0.0434912709340626</v>
       </c>
       <c r="AD7">
-        <v>1761.4</v>
+        <v>12.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1761.4</v>
+        <v>12.9</v>
       </c>
       <c r="AG7">
-        <v>1753.6</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>0.706056840501864</v>
+        <v>0.1146666666666667</v>
       </c>
       <c r="AI7">
-        <v>0.7605025689737057</v>
+        <v>0.2320143884892086</v>
       </c>
       <c r="AJ7">
-        <v>0.70513490691222</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.7596932807693973</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.773</v>
+      </c>
+      <c r="AN7">
+        <v>2.590361445783132</v>
+      </c>
+      <c r="AO7">
+        <v>6.129032258064516</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>6.144890038809832</v>
       </c>
     </row>
     <row r="8">
@@ -1338,121 +1362,1252 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Nextgreen Global Berhad (KLSE:NGGB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0.6208991494532199</v>
+      </c>
+      <c r="H8">
+        <v>0.6208991494532199</v>
+      </c>
+      <c r="I8">
+        <v>0.5346294046172539</v>
+      </c>
+      <c r="J8">
+        <v>0.4912597626497776</v>
+      </c>
+      <c r="K8">
+        <v>3.15</v>
+      </c>
+      <c r="L8">
+        <v>0.3827460510328068</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1.76</v>
+      </c>
+      <c r="V8">
+        <v>0.009366684406599254</v>
+      </c>
+      <c r="W8">
+        <v>0.05779816513761468</v>
+      </c>
+      <c r="X8">
+        <v>0.05497647492454955</v>
+      </c>
+      <c r="Y8">
+        <v>0.002821690213065123</v>
+      </c>
+      <c r="Z8">
+        <v>0.1194242098847839</v>
+      </c>
+      <c r="AA8">
+        <v>0.05866830900263618</v>
+      </c>
+      <c r="AB8">
+        <v>0.05464130782336643</v>
+      </c>
+      <c r="AC8">
+        <v>0.004027001179269754</v>
+      </c>
+      <c r="AD8">
+        <v>15.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>15.6</v>
+      </c>
+      <c r="AG8">
+        <v>13.84</v>
+      </c>
+      <c r="AH8">
+        <v>0.07665847665847665</v>
+      </c>
+      <c r="AI8">
+        <v>0.1916461916461916</v>
+      </c>
+      <c r="AJ8">
+        <v>0.06860315257261822</v>
+      </c>
+      <c r="AK8">
+        <v>0.1737820190858865</v>
+      </c>
+      <c r="AL8">
+        <v>0.925</v>
+      </c>
+      <c r="AM8">
+        <v>0.925</v>
+      </c>
+      <c r="AN8">
+        <v>2.765957446808511</v>
+      </c>
+      <c r="AO8">
+        <v>4.756756756756757</v>
+      </c>
+      <c r="AP8">
+        <v>2.453900709219858</v>
+      </c>
+      <c r="AQ8">
+        <v>4.756756756756757</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fima Corporation Berhad (KLSE:FIMACOR)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.00411</v>
+      </c>
+      <c r="E9">
+        <v>-0.113</v>
+      </c>
+      <c r="G9">
+        <v>0.2282003710575139</v>
+      </c>
+      <c r="H9">
+        <v>0.2282003710575139</v>
+      </c>
+      <c r="I9">
+        <v>0.1350649350649351</v>
+      </c>
+      <c r="J9">
+        <v>0.1028446252542638</v>
+      </c>
+      <c r="K9">
+        <v>5.77</v>
+      </c>
+      <c r="L9">
+        <v>0.1070500927643785</v>
+      </c>
+      <c r="M9">
+        <v>6.396</v>
+      </c>
+      <c r="N9">
+        <v>0.06952173913043479</v>
+      </c>
+      <c r="O9">
+        <v>1.108492201039861</v>
+      </c>
+      <c r="P9">
+        <v>6.31</v>
+      </c>
+      <c r="Q9">
+        <v>0.06858695652173913</v>
+      </c>
+      <c r="R9">
+        <v>1.093587521663778</v>
+      </c>
+      <c r="S9">
+        <v>0.0860000000000003</v>
+      </c>
+      <c r="T9">
+        <v>0.01344590368980618</v>
+      </c>
+      <c r="U9">
+        <v>14.7</v>
+      </c>
+      <c r="V9">
+        <v>0.1597826086956522</v>
+      </c>
+      <c r="W9">
+        <v>0.04664510913500404</v>
+      </c>
+      <c r="X9">
+        <v>0.05617840874115658</v>
+      </c>
+      <c r="Y9">
+        <v>-0.00953329960615254</v>
+      </c>
+      <c r="Z9">
+        <v>0.4143285417787686</v>
+      </c>
+      <c r="AA9">
+        <v>0.04261146361138305</v>
+      </c>
+      <c r="AB9">
+        <v>0.0542851950257713</v>
+      </c>
+      <c r="AC9">
+        <v>-0.01167373141438825</v>
+      </c>
+      <c r="AD9">
+        <v>17.2</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>17.2</v>
+      </c>
+      <c r="AG9">
+        <v>2.5</v>
+      </c>
+      <c r="AH9">
+        <v>0.1575091575091575</v>
+      </c>
+      <c r="AI9">
+        <v>0.1198606271777003</v>
+      </c>
+      <c r="AJ9">
+        <v>0.02645502645502645</v>
+      </c>
+      <c r="AK9">
+        <v>0.01940993788819876</v>
+      </c>
+      <c r="AL9">
+        <v>0.482</v>
+      </c>
+      <c r="AM9">
+        <v>-0.798</v>
+      </c>
+      <c r="AN9">
+        <v>1.853448275862069</v>
+      </c>
+      <c r="AO9">
+        <v>15.10373443983403</v>
+      </c>
+      <c r="AP9">
+        <v>0.269396551724138</v>
+      </c>
+      <c r="AQ9">
+        <v>-9.12280701754386</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tien Wah Press Holdings Berhad (KLSE:TIENWAH)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.05889999999999999</v>
+      </c>
+      <c r="G10">
+        <v>0.1517304189435337</v>
+      </c>
+      <c r="H10">
+        <v>0.1517304189435337</v>
+      </c>
+      <c r="I10">
+        <v>0.0460702901485911</v>
+      </c>
+      <c r="J10">
+        <v>0.0460702901485911</v>
+      </c>
+      <c r="K10">
+        <v>-2.18</v>
+      </c>
+      <c r="L10">
+        <v>-0.03970856102003643</v>
+      </c>
+      <c r="M10">
+        <v>1.73</v>
+      </c>
+      <c r="N10">
+        <v>0.0647940074906367</v>
+      </c>
+      <c r="O10">
+        <v>-0.7935779816513761</v>
+      </c>
+      <c r="P10">
+        <v>1.73</v>
+      </c>
+      <c r="Q10">
+        <v>0.0647940074906367</v>
+      </c>
+      <c r="R10">
+        <v>-0.7935779816513761</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>5.85</v>
+      </c>
+      <c r="V10">
+        <v>0.2191011235955056</v>
+      </c>
+      <c r="W10">
+        <v>-0.0339035769828927</v>
+      </c>
+      <c r="X10">
+        <v>0.06111255314612214</v>
+      </c>
+      <c r="Y10">
+        <v>-0.09501613012901483</v>
+      </c>
+      <c r="Z10">
+        <v>0.7581437758426609</v>
+      </c>
+      <c r="AA10">
+        <v>0.0349279037274198</v>
+      </c>
+      <c r="AB10">
+        <v>0.05466540840425675</v>
+      </c>
+      <c r="AC10">
+        <v>-0.01973750467683695</v>
+      </c>
+      <c r="AD10">
+        <v>16</v>
+      </c>
+      <c r="AE10">
+        <v>0.3837053542117431</v>
+      </c>
+      <c r="AF10">
+        <v>16.38370535421174</v>
+      </c>
+      <c r="AG10">
+        <v>10.53370535421174</v>
+      </c>
+      <c r="AH10">
+        <v>0.3802761442989517</v>
+      </c>
+      <c r="AI10">
+        <v>0.1894426850365502</v>
+      </c>
+      <c r="AJ10">
+        <v>0.2829077915829886</v>
+      </c>
+      <c r="AK10">
+        <v>0.1306365037788944</v>
+      </c>
+      <c r="AL10">
+        <v>0.705</v>
+      </c>
+      <c r="AM10">
+        <v>0.6759999999999999</v>
+      </c>
+      <c r="AN10">
+        <v>1.704666524611123</v>
+      </c>
+      <c r="AO10">
+        <v>3.120567375886525</v>
+      </c>
+      <c r="AP10">
+        <v>1.122278431090107</v>
+      </c>
+      <c r="AQ10">
+        <v>3.254437869822486</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ELK-Desa Resources Berhad (KLSE:ELKDESA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.0262</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>7.66</v>
+      </c>
+      <c r="L11">
+        <v>0.285820895522388</v>
+      </c>
+      <c r="M11">
+        <v>6.3</v>
+      </c>
+      <c r="N11">
+        <v>0.05084745762711864</v>
+      </c>
+      <c r="O11">
+        <v>0.8224543080939948</v>
+      </c>
+      <c r="P11">
+        <v>6.3</v>
+      </c>
+      <c r="Q11">
+        <v>0.05084745762711864</v>
+      </c>
+      <c r="R11">
+        <v>0.8224543080939948</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1.94</v>
+      </c>
+      <c r="V11">
+        <v>0.01565778853914447</v>
+      </c>
+      <c r="W11">
+        <v>0.07629482071713146</v>
+      </c>
+      <c r="X11">
+        <v>0.05904721816033075</v>
+      </c>
+      <c r="Y11">
+        <v>0.01724760255680072</v>
+      </c>
+      <c r="Z11">
+        <v>0.1956632839307878</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05453377066921195</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05453377066921195</v>
+      </c>
+      <c r="AD11">
+        <v>53.9</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>53.9</v>
+      </c>
+      <c r="AG11">
+        <v>51.96</v>
+      </c>
+      <c r="AH11">
+        <v>0.3031496062992126</v>
+      </c>
+      <c r="AI11">
+        <v>0.3484162895927602</v>
+      </c>
+      <c r="AJ11">
+        <v>0.2954622995564654</v>
+      </c>
+      <c r="AK11">
+        <v>0.3401413982717989</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RCE Capital Berhad (KLSE:RCECAP)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.101</v>
+      </c>
+      <c r="E12">
+        <v>0.0941</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>30.9</v>
+      </c>
+      <c r="L12">
+        <v>0.5908221797323135</v>
+      </c>
+      <c r="M12">
+        <v>46.8</v>
+      </c>
+      <c r="N12">
+        <v>0.09574468085106382</v>
+      </c>
+      <c r="O12">
+        <v>1.514563106796116</v>
+      </c>
+      <c r="P12">
+        <v>46.8</v>
+      </c>
+      <c r="Q12">
+        <v>0.09574468085106382</v>
+      </c>
+      <c r="R12">
+        <v>1.514563106796116</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>19.2</v>
+      </c>
+      <c r="V12">
+        <v>0.03927986906710311</v>
+      </c>
+      <c r="W12">
+        <v>0.1574923547400612</v>
+      </c>
+      <c r="X12">
+        <v>0.06481898312119652</v>
+      </c>
+      <c r="Y12">
+        <v>0.09267337161886463</v>
+      </c>
+      <c r="Z12">
+        <v>0.09240282685512367</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05484068411965931</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05484068411965931</v>
+      </c>
+      <c r="AD12">
+        <v>456.6</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>456.6</v>
+      </c>
+      <c r="AG12">
+        <v>437.4</v>
+      </c>
+      <c r="AH12">
+        <v>0.4829701713560398</v>
+      </c>
+      <c r="AI12">
+        <v>0.7220113851992409</v>
+      </c>
+      <c r="AJ12">
+        <v>0.47225221334485</v>
+      </c>
+      <c r="AK12">
+        <v>0.713307240704501</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AEON Credit Service (M) Berhad (KLSE:AEONCR)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0667</v>
+      </c>
+      <c r="E13">
+        <v>0.0277</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>85.8</v>
+      </c>
+      <c r="L13">
+        <v>0.2723809523809524</v>
+      </c>
+      <c r="M13">
+        <v>32.7</v>
+      </c>
+      <c r="N13">
+        <v>0.05274193548387097</v>
+      </c>
+      <c r="O13">
+        <v>0.3811188811188811</v>
+      </c>
+      <c r="P13">
+        <v>32.7</v>
+      </c>
+      <c r="Q13">
+        <v>0.05274193548387097</v>
+      </c>
+      <c r="R13">
+        <v>0.3811188811188811</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>26.9</v>
+      </c>
+      <c r="V13">
+        <v>0.04338709677419355</v>
+      </c>
+      <c r="W13">
+        <v>0.1546782044348296</v>
+      </c>
+      <c r="X13">
+        <v>0.09023729245341525</v>
+      </c>
+      <c r="Y13">
+        <v>0.06444091198141438</v>
+      </c>
+      <c r="Z13">
+        <v>0.136470863470649</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05531008501224075</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05531008501224075</v>
+      </c>
+      <c r="AD13">
+        <v>1941.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1941.9</v>
+      </c>
+      <c r="AG13">
+        <v>1915</v>
+      </c>
+      <c r="AH13">
+        <v>0.75799211522698</v>
+      </c>
+      <c r="AI13">
+        <v>0.7696179454660749</v>
+      </c>
+      <c r="AJ13">
+        <v>0.7554240631163708</v>
+      </c>
+      <c r="AK13">
+        <v>0.7671353603332932</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Computer Forms (Malaysia) Berhad (KLSE:CFM)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>-0.2932454695222405</v>
+      </c>
+      <c r="H14">
+        <v>-0.2932454695222405</v>
+      </c>
+      <c r="I14">
+        <v>-0.3113673805601317</v>
+      </c>
+      <c r="J14">
+        <v>-0.3113673805601317</v>
+      </c>
+      <c r="K14">
+        <v>-1.88</v>
+      </c>
+      <c r="L14">
+        <v>-0.3097199341021417</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0.36</v>
+      </c>
+      <c r="V14">
+        <v>0.03529411764705882</v>
+      </c>
+      <c r="W14">
+        <v>-0.0964102564102564</v>
+      </c>
+      <c r="X14">
+        <v>0.05561497525967953</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1520252316699359</v>
+      </c>
+      <c r="Z14">
+        <v>0.3235607675906184</v>
+      </c>
+      <c r="AA14">
+        <v>-0.1007462686567164</v>
+      </c>
+      <c r="AB14">
+        <v>0.05568530375219539</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1564315724089118</v>
+      </c>
+      <c r="AD14">
+        <v>1.41</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1.41</v>
+      </c>
+      <c r="AG14">
+        <v>1.05</v>
+      </c>
+      <c r="AH14">
+        <v>0.1214470284237726</v>
+      </c>
+      <c r="AI14">
+        <v>0.0499822757887274</v>
+      </c>
+      <c r="AJ14">
+        <v>0.09333333333333332</v>
+      </c>
+      <c r="AK14">
+        <v>0.03770197486535008</v>
+      </c>
+      <c r="AL14">
+        <v>0.053</v>
+      </c>
+      <c r="AM14">
+        <v>0.053</v>
+      </c>
+      <c r="AN14">
+        <v>-0.7921348314606741</v>
+      </c>
+      <c r="AO14">
+        <v>-35.66037735849056</v>
+      </c>
+      <c r="AP14">
+        <v>-0.5898876404494381</v>
+      </c>
+      <c r="AQ14">
+        <v>-35.66037735849056</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Johan Holdings Berhad (KLSE:JOHAN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G8">
-        <v>-0.6571428571428571</v>
-      </c>
-      <c r="H8">
-        <v>-0.6571428571428571</v>
-      </c>
-      <c r="I8">
-        <v>-0.7676190476190476</v>
-      </c>
-      <c r="J8">
-        <v>-0.7676190476190476</v>
-      </c>
-      <c r="K8">
-        <v>-4.98</v>
-      </c>
-      <c r="L8">
-        <v>-0.9485714285714286</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>8.94</v>
-      </c>
-      <c r="V8">
-        <v>0.6081632653061224</v>
-      </c>
-      <c r="W8">
-        <v>-0.08721541155866901</v>
-      </c>
-      <c r="X8">
-        <v>0.05175644286885151</v>
-      </c>
-      <c r="Y8">
-        <v>-0.1389718544275205</v>
-      </c>
-      <c r="Z8">
-        <v>0.1422340223781529</v>
-      </c>
-      <c r="AA8">
-        <v>-0.109181544796944</v>
-      </c>
-      <c r="AB8">
-        <v>0.05179911374242892</v>
-      </c>
-      <c r="AC8">
-        <v>-0.1609806585393729</v>
-      </c>
-      <c r="AD8">
+      <c r="G15">
+        <v>-1.051181102362205</v>
+      </c>
+      <c r="H15">
+        <v>-1.051181102362205</v>
+      </c>
+      <c r="I15">
+        <v>-1.041338582677165</v>
+      </c>
+      <c r="J15">
+        <v>-1.041338582677165</v>
+      </c>
+      <c r="K15">
+        <v>-7.89</v>
+      </c>
+      <c r="L15">
+        <v>-1.553149606299213</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>11.5</v>
+      </c>
+      <c r="V15">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="W15">
+        <v>-0.1661052631578947</v>
+      </c>
+      <c r="X15">
+        <v>0.05432194359363328</v>
+      </c>
+      <c r="Y15">
+        <v>-0.220427206751528</v>
+      </c>
+      <c r="Z15">
+        <v>0.1299033396409758</v>
+      </c>
+      <c r="AA15">
+        <v>-0.1352733595867642</v>
+      </c>
+      <c r="AB15">
+        <v>0.05417401559689437</v>
+      </c>
+      <c r="AC15">
+        <v>-0.1894473751836586</v>
+      </c>
+      <c r="AD15">
+        <v>0.436</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0.436</v>
+      </c>
+      <c r="AG15">
+        <v>-11.064</v>
+      </c>
+      <c r="AH15">
+        <v>0.02574397732640529</v>
+      </c>
+      <c r="AI15">
+        <v>0.01015464877957891</v>
+      </c>
+      <c r="AJ15">
+        <v>-2.035320088300221</v>
+      </c>
+      <c r="AK15">
+        <v>-0.3519531747041608</v>
+      </c>
+      <c r="AL15">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM15">
+        <v>-0.248</v>
+      </c>
+      <c r="AN15">
+        <v>-0.09198312236286919</v>
+      </c>
+      <c r="AO15">
+        <v>-61.51162790697675</v>
+      </c>
+      <c r="AP15">
+        <v>2.334177215189873</v>
+      </c>
+      <c r="AQ15">
+        <v>21.33064516129032</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pertama Digital Berhad (KLSE:PERTAMA)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>-1.877868852459016</v>
+      </c>
+      <c r="H16">
+        <v>-1.950819672131147</v>
+      </c>
+      <c r="I16">
+        <v>-2.147540983606557</v>
+      </c>
+      <c r="J16">
+        <v>-2.147540983606557</v>
+      </c>
+      <c r="K16">
+        <v>-9.92</v>
+      </c>
+      <c r="L16">
+        <v>-8.131147540983607</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>33.2</v>
+      </c>
+      <c r="V16">
+        <v>0.1331728840754112</v>
+      </c>
+      <c r="W16">
+        <v>-0.8406779661016949</v>
+      </c>
+      <c r="X16">
+        <v>0.05409522111815167</v>
+      </c>
+      <c r="Y16">
+        <v>-0.8947731872198466</v>
+      </c>
+      <c r="Z16">
+        <v>0.09822866344605473</v>
+      </c>
+      <c r="AA16">
+        <v>-0.2109500805152979</v>
+      </c>
+      <c r="AB16">
+        <v>0.05407157717911076</v>
+      </c>
+      <c r="AC16">
+        <v>-0.2650216576944087</v>
+      </c>
+      <c r="AD16">
+        <v>1.7</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.7</v>
+      </c>
+      <c r="AG16">
+        <v>-31.5</v>
+      </c>
+      <c r="AH16">
+        <v>0.006772908366533864</v>
+      </c>
+      <c r="AI16">
+        <v>0.346938775510204</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.1446280991735537</v>
+      </c>
+      <c r="AK16">
+        <v>1.113074204946996</v>
+      </c>
+      <c r="AL16">
+        <v>0.089</v>
+      </c>
+      <c r="AM16">
+        <v>0.089</v>
+      </c>
+      <c r="AN16">
+        <v>-0.6538461538461539</v>
+      </c>
+      <c r="AO16">
+        <v>-29.43820224719101</v>
+      </c>
+      <c r="AP16">
+        <v>12.11538461538462</v>
+      </c>
+      <c r="AQ16">
+        <v>-29.43820224719101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Revenue Group Berhad (KLSE:REVENUE)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>-0.1289237668161435</v>
+      </c>
+      <c r="H17">
+        <v>-0.1289237668161435</v>
+      </c>
+      <c r="I17">
+        <v>-0.1603139013452915</v>
+      </c>
+      <c r="J17">
+        <v>-0.1603139013452915</v>
+      </c>
+      <c r="K17">
+        <v>-14.2</v>
+      </c>
+      <c r="L17">
+        <v>-0.1591928251121076</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>5.51</v>
+      </c>
+      <c r="V17">
+        <v>0.2230769230769231</v>
+      </c>
+      <c r="W17">
+        <v>-0.4290030211480362</v>
+      </c>
+      <c r="X17">
+        <v>0.05822076006537703</v>
+      </c>
+      <c r="Y17">
+        <v>-0.4872237812134133</v>
+      </c>
+      <c r="Z17">
+        <v>3.623070674248578</v>
+      </c>
+      <c r="AA17">
+        <v>-0.5808285946385052</v>
+      </c>
+      <c r="AB17">
+        <v>0.05564915869036315</v>
+      </c>
+      <c r="AC17">
+        <v>-0.6364777533288684</v>
+      </c>
+      <c r="AD17">
+        <v>8.98</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>8.98</v>
+      </c>
+      <c r="AG17">
+        <v>3.470000000000001</v>
+      </c>
+      <c r="AH17">
+        <v>0.2666270783847981</v>
+      </c>
+      <c r="AI17">
+        <v>0.2604408352668213</v>
+      </c>
+      <c r="AJ17">
+        <v>0.1231806886758964</v>
+      </c>
+      <c r="AK17">
+        <v>0.1197790818087677</v>
+      </c>
+      <c r="AL17">
         <v>0.546</v>
       </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
+      <c r="AM17">
         <v>0.546</v>
       </c>
-      <c r="AG8">
-        <v>-8.394</v>
-      </c>
-      <c r="AH8">
-        <v>0.03581267217630855</v>
-      </c>
-      <c r="AI8">
-        <v>0.01017783245721955</v>
-      </c>
-      <c r="AJ8">
-        <v>-1.331113225499524</v>
-      </c>
-      <c r="AK8">
-        <v>-0.1877600322104415</v>
-      </c>
-      <c r="AL8">
-        <v>0.202</v>
-      </c>
-      <c r="AM8">
-        <v>0.202</v>
-      </c>
-      <c r="AN8">
-        <v>-0.1475675675675676</v>
-      </c>
-      <c r="AO8">
-        <v>-19.95049504950495</v>
-      </c>
-      <c r="AP8">
-        <v>2.268648648648649</v>
-      </c>
-      <c r="AQ8">
-        <v>-19.95049504950495</v>
+      <c r="AN17">
+        <v>-0.7808695652173914</v>
+      </c>
+      <c r="AO17">
+        <v>-26.19047619047619</v>
+      </c>
+      <c r="AP17">
+        <v>-0.3017391304347827</v>
+      </c>
+      <c r="AQ17">
+        <v>-26.19047619047619</v>
       </c>
     </row>
   </sheetData>
